--- a/Health/src/test/resources/LoginData.xlsx
+++ b/Health/src/test/resources/LoginData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\automationtesting\projects\Health\Health\src\test\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ELCOT\Downloads\My_Website\CuraHealthAutomationFramework\Health\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62CB4970-E8F6-4E08-AEBD-11262A8ABC24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BE07778-2A79-4C34-8E9D-C780CFA83242}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{1685983E-8C2D-4DA6-AA57-388C7E0B0289}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{1685983E-8C2D-4DA6-AA57-388C7E0B0289}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
   <si>
     <t>Username</t>
   </si>
@@ -49,6 +49,15 @@
   </si>
   <si>
     <t>ThisIsNotPassword</t>
+  </si>
+  <si>
+    <t>ExpectedResult</t>
+  </si>
+  <si>
+    <t>Valid</t>
+  </si>
+  <si>
+    <t>Invalid</t>
   </si>
 </sst>
 </file>
@@ -104,9 +113,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -144,7 +153,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -250,7 +259,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -392,7 +401,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -400,31 +409,40 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44D31C4C-23C9-4741-B3D3-B45A60495566}">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
       </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
       <c r="B3" t="s">
         <v>4</v>
+      </c>
+      <c r="C3" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
